--- a/jogos_2024-10-15.xlsx
+++ b/jogos_2024-10-15.xlsx
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>1.05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>14.46</v>
       </c>
       <c r="N4" t="n">
-        <v>1.38</v>
+        <v>21.57</v>
       </c>
       <c r="O4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['5', '14', '41', '55', '72']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['11', '57']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.29</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45580.65625</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>6.6</v>
+        <v>2.79</v>
       </c>
       <c r="O5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['11', '44']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['53', '57', '69', '80']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.73</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="AJ5" t="n">
         <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['23', '29', '34', '82']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45580.65625</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>6.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,31 +1353,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['11', '44']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['53', '57', '69', '80']</t>
+          <t>['23', '29', '34', '82']</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45580.65625</v>
@@ -1417,63 +1417,63 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="M8" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="N8" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1482,44 +1482,44 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>1.81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['5', '14', '41', '55', '72']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>7</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45580.65625</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,70 +1572,70 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '57']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.8</v>
+        <v>4.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45580.65625</v>
